--- a/archive/XrayAbsorbtion/cdif4xas-mappings.sssom.xlsx
+++ b/archive/XrayAbsorbtion/cdif4xas-mappings.sssom.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/944a82e2ddcde9eb/Documents/GithubC/CDIF/integration/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GithubC\CDIF\profile-datastructure\archive\XrayAbsorbtion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{2C5C2F34-77B0-4F5A-B92F-1753A983E05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DB631AE-D9E0-480F-9C46-4416C8622A52}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3B0761-D5D8-4110-A054-1C8F2C34FBD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1035" windowWidth="18592" windowHeight="9045" xr2:uid="{95531538-5F64-46B5-81A1-9BFC747EF024}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="26220" windowHeight="14775" xr2:uid="{95531538-5F64-46B5-81A1-9BFC747EF024}"/>
   </bookViews>
   <sheets>
     <sheet name="cdif4xas-mappings.sssom" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -242,7 +255,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -376,12 +389,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1124,19 +1131,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55FD8C94-0288-4984-A097-29E75AEEB2EC}">
   <dimension ref="A1:K27"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.06640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" customWidth="1"/>
-    <col min="3" max="3" width="24.265625" customWidth="1"/>
-    <col min="4" max="4" width="30.265625" customWidth="1"/>
-    <col min="5" max="5" width="23.6640625" customWidth="1"/>
-    <col min="6" max="6" width="26.796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="50.140625" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" customWidth="1"/>
+    <col min="4" max="4" width="30.28515625" customWidth="1"/>
+    <col min="5" max="5" width="23.7109375" customWidth="1"/>
+    <col min="6" max="6" width="34.85546875" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1171,7 +1178,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1200,7 +1207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -1229,7 +1236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -1258,7 +1265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -1287,7 +1294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1316,7 +1323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1345,7 +1352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -1374,7 +1381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -1400,7 +1407,7 @@
         <v>45814</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -1429,7 +1436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -1458,7 +1465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -1481,7 +1488,7 @@
         <v>45828</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -1504,7 +1511,7 @@
         <v>45828</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -1527,7 +1534,7 @@
         <v>45828</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -1550,7 +1557,7 @@
         <v>45828</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -1573,7 +1580,7 @@
         <v>45828</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1596,7 +1603,7 @@
         <v>45828</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1619,7 +1626,7 @@
         <v>45828</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -1642,7 +1649,7 @@
         <v>45828</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>50</v>
       </c>
@@ -1665,7 +1672,7 @@
         <v>45828</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -1688,7 +1695,7 @@
         <v>45828</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -1711,7 +1718,7 @@
         <v>45828</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>56</v>
       </c>
@@ -1734,7 +1741,7 @@
         <v>45828</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -1757,7 +1764,7 @@
         <v>45828</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -1780,7 +1787,7 @@
         <v>45828</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1803,7 +1810,7 @@
         <v>45828</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>64</v>
       </c>
